--- a/input/data/original/Data_centers_Chile_07062026.xlsx
+++ b/input/data/original/Data_centers_Chile_07062026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="423">
   <si>
     <t xml:space="preserve">operador</t>
   </si>
@@ -1277,6 +1277,18 @@
   </si>
   <si>
     <t xml:space="preserve">https://seia.sea.gob.cl/archivos/2022/07/26/7450_CAP._I_Descripcion_del_Proyecto_EMI_0.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nodo Pacífico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center El Piñeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundo El Piñeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://roadshow.cl/un-nuevo-data-center-aterriza-en-chile-se-levantara-en-san-antonio-con-una-inversion-de-us262-millones/</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1298,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1327,7 +1339,7 @@
     <font>
       <u val="single"/>
       <sz val="11"/>
-      <color rgb="FFCECEFA"/>
+      <color rgb="FFCFCFFB"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1338,12 +1350,6 @@
       <name val="Calibri"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1394,7 +1400,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1420,14 +1426,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1465,7 +1463,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCECEFA"/>
+      <rgbColor rgb="FFCFCFFB"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -4325,7 +4323,7 @@
       <c r="K91" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="L91" s="7" t="s">
+      <c r="L91" s="3" t="s">
         <v>412</v>
       </c>
     </row>
@@ -4359,7 +4357,7 @@
       <c r="A93" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="6" t="s">
         <v>416</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -4381,7 +4379,32 @@
         <v>418</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H94" s="1">
+        <v>70</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5421,6 +5444,7 @@
     <hyperlink ref="J89" r:id="rId110" display="https://www.biobiochile.cl/noticias/nacional/chile/2026/09/04/organizaciones-buscan-frenar-plan-de-google-para-instalar-data-center-sin-evaluacion-ambiental-cerrillos.shtml"/>
     <hyperlink ref="J91" r:id="rId111" display="https://eldesconcierto.cl/reportajes/el-boom-los-data-centers-y-el-cambio-ambiental-siete-proyectos-buscan-avanzar-ingresar-al-seia-n5462381"/>
     <hyperlink ref="K91" r:id="rId112" display="https://pertinencia.sea.gob.cl/api/public/expediente/PERTI-2026-9361"/>
+    <hyperlink ref="J94" r:id="rId113" display="https://roadshow.cl/un-nuevo-data-center-aterriza-en-chile-se-levantara-en-san-antonio-con-una-inversion-de-us262-millones/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
